--- a/sources/jun_step3.xlsx
+++ b/sources/jun_step3.xlsx
@@ -732,6 +732,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>c3fb2b44-9abc-4fc9-8f10-b2e01504275a</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>c3fb2b44-9abc-4fc9-8f10-b2e01504275a</t>
@@ -769,6 +774,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4e122e09-243f-49b9-96ea-c109b7d9a02f</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>4e122e09-243f-49b9-96ea-c109b7d9a02f</t>
@@ -804,6 +814,11 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>30e2beaa-6d7c-42d2-8397-096837f7826d</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -5655,6 +5670,11 @@
           <t>mhmmmlmlmm</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>fcd205b6-5f94-4cfd-a61b-4cc522dbe599</t>
+        </is>
+      </c>
       <c r="O108" t="inlineStr">
         <is>
           <t>fcd205b6-5f94-4cfd-a61b-4cc522dbe599</t>
@@ -5682,6 +5702,11 @@
           <t>mhmmmlhhlh</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>91ec0924-2220-448a-88fb-9b64f00b6f0c</t>
+        </is>
+      </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>91ec0924-2220-448a-88fb-9b64f00b6f0c</t>
@@ -5707,6 +5732,11 @@
       <c r="I110" t="inlineStr">
         <is>
           <t>mhmm</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>77355c32-3a7d-4d9f-8a8d-7ff03658cb77</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
